--- a/output/pdf_financials_xlsx/WISR.xlsx
+++ b/output/pdf_financials_xlsx/WISR.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="24">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="28">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="30">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.110797</v>
+        <v>-0.110797</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1.503246</v>
+        <v>-1.503246</v>
       </c>
     </row>
     <row r="45">

--- a/output/pdf_financials_xlsx/WISR.xlsx
+++ b/output/pdf_financials_xlsx/WISR.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.031525</v>
+        <v>0.057233</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.128554</v>
+        <v>0.288153</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.031525</v>
+        <v>0.057233</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.241515</v>
+        <v>0.401114</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.031525</v>
+        <v>-0.057233</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.241515</v>
+        <v>-0.401114</v>
       </c>
     </row>
     <row r="12">
@@ -3112,7 +3112,11 @@
           <t>Subscription receipts applied to private placement $</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -3216,7 +3220,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.025708</v>
       </c>
